--- a/survey_templates/043_technical_mapping_survey--survey_templates.xlsx
+++ b/survey_templates/043_technical_mapping_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1148,233 +1148,233 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>project_types</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Project types</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>project_types_choices</t>
+          <t>challenges_faced_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>project_types</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Project types</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>project_types_choices</t>
+          <t>challenges_faced_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>project_types</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Project types</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>project_types_choices</t>
+          <t>challenges_faced_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project_types</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Project types</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>project_types_choices</t>
+          <t>challenges_faced_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>project_types</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Project types</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>project_types_choices</t>
+          <t>challenges_faced_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project_types</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Project types</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>project_types_choices</t>
+          <t>project_tools_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project_types</t>
+          <t>project_tools_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Project types</t>
+          <t>project tools 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>project_types_choices</t>
+          <t>project_tools_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>project_types</t>
+          <t>project_tools_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Project types</t>
+          <t>project tools 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>project_types_choices</t>
+          <t>project_tools_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>project_types</t>
+          <t>project_tools_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Project types</t>
+          <t>project tools 3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>challenges_faced_choices</t>
+          <t>project_tools_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>project_tools_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>project tools 4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>challenges_faced_choices</t>
+          <t>project_tools_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>project_tools_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>project tools 5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>challenges_faced_choices</t>
+          <t>project_tools_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>project_tools_6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>project tools 6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>challenges_faced_choices</t>
+          <t>project_tools_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>project_tools_7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>project tools 7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>challenges_faced_choices</t>
+          <t>project_tools_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>project_tools_8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>project tools 8</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project_tools_9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project tools 9</t>
         </is>
       </c>
     </row>
@@ -1403,148 +1403,148 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project_tools_10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project tools 10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>project_tools_choices</t>
+          <t>project_tools_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project_tools_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project tools 1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>project_tools_choices</t>
+          <t>project_tools_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project_tools_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project tools 2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>project_tools_choices</t>
+          <t>project_tools_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project_tools_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project tools 3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>project_tools_choices</t>
+          <t>project_tools_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project_tools_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project tools 4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>project_tools_choices</t>
+          <t>project_tools_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project_tools_5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project tools 5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>project_tools_choices</t>
+          <t>project_tools_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project_tools_6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project tools 6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>project_tools_choices</t>
+          <t>project_tools_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project_tools_7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project tools 7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>project_tools_choices</t>
+          <t>project_tools_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project_tools_8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project tools 8</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project_tools_9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project tools 9</t>
         </is>
       </c>
     </row>
@@ -1573,148 +1573,148 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project_tools_10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project tools 10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>project_tools_2_choices</t>
+          <t>project_tools_3_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project_tools_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project tools 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>project_tools_2_choices</t>
+          <t>project_tools_3_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project_tools_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project tools 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>project_tools_2_choices</t>
+          <t>project_tools_3_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project_tools_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project tools 3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>project_tools_2_choices</t>
+          <t>project_tools_3_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project_tools_4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project tools 4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>project_tools_2_choices</t>
+          <t>project_tools_3_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project_tools_5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project tools 5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>project_tools_2_choices</t>
+          <t>project_tools_3_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project_tools_6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project tools 6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>project_tools_2_choices</t>
+          <t>project_tools_3_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project_tools_7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project tools 7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>project_tools_2_choices</t>
+          <t>project_tools_3_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project_tools_8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project tools 8</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project_tools_9</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project tools 9</t>
         </is>
       </c>
     </row>
@@ -1743,148 +1743,148 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project_tools_10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project tools 10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>project_tools_3_choices</t>
+          <t>project_tools_4_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project_tools_1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project tools 1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>project_tools_3_choices</t>
+          <t>project_tools_4_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project_tools_2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project tools 2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>project_tools_3_choices</t>
+          <t>project_tools_4_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project_tools_3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project tools 3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>project_tools_3_choices</t>
+          <t>project_tools_4_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project_tools_4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project tools 4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>project_tools_3_choices</t>
+          <t>project_tools_4_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project_tools_5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project tools 5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>project_tools_3_choices</t>
+          <t>project_tools_4_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project_tools_6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project tools 6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>project_tools_3_choices</t>
+          <t>project_tools_4_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project_tools_7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project tools 7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>project_tools_3_choices</t>
+          <t>project_tools_4_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project_tools_8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project tools 8</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project_tools_9</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project tools 9</t>
         </is>
       </c>
     </row>
@@ -1913,148 +1913,148 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project_tools_10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project tools 10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>project_tools_4_choices</t>
+          <t>project_tools_5_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project_tools_1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project tools 1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>project_tools_4_choices</t>
+          <t>project_tools_5_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project_tools_2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project tools 2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>project_tools_4_choices</t>
+          <t>project_tools_5_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project_tools_3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project tools 3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>project_tools_4_choices</t>
+          <t>project_tools_5_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project_tools_4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project tools 4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>project_tools_4_choices</t>
+          <t>project_tools_5_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project_tools_5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project tools 5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>project_tools_4_choices</t>
+          <t>project_tools_5_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project_tools_6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project tools 6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>project_tools_4_choices</t>
+          <t>project_tools_5_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project_tools_7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project tools 7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>project_tools_4_choices</t>
+          <t>project_tools_5_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project_tools_8</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project tools 8</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project_tools_9</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project tools 9</t>
         </is>
       </c>
     </row>
@@ -2083,488 +2083,488 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project_tools_10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project tools 10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>project_tools_5_choices</t>
+          <t>project_challenges_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>project_tools_5_choices</t>
+          <t>project_challenges_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>project_tools_5_choices</t>
+          <t>project_challenges_2_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>project_tools_5_choices</t>
+          <t>project_challenges_2_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>project_tools_5_choices</t>
+          <t>project_challenges_2_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>project_tools_5_choices</t>
+          <t>project_challenges_3_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>project_tools_5_choices</t>
+          <t>project_challenges_3_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>project_tools_5_choices</t>
+          <t>project_challenges_3_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>project_challenges_2_choices</t>
+          <t>project_challenges_3_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>project_challenges_2_choices</t>
+          <t>project_challenges_3_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>project_challenges_2_choices</t>
+          <t>project_challenges_4_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>project_challenges_2_choices</t>
+          <t>project_challenges_4_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>project_challenges_2_choices</t>
+          <t>project_challenges_4_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>project_challenges_3_choices</t>
+          <t>project_challenges_4_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>project_challenges_3_choices</t>
+          <t>project_challenges_4_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>project_challenges_3_choices</t>
+          <t>project_challenges_5_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>project_challenges_3_choices</t>
+          <t>project_challenges_5_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>project_challenges_3_choices</t>
+          <t>project_challenges_5_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>project_challenges_4_choices</t>
+          <t>project_challenges_5_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>project_challenges_4_choices</t>
+          <t>project_challenges_5_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>project_challenges_4_choices</t>
+          <t>project_tools_7_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>project_tools_1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>project tools 1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>project_challenges_4_choices</t>
+          <t>project_tools_7_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>project_tools_2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>project tools 2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>project_challenges_4_choices</t>
+          <t>project_tools_7_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>project_tools_3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>project tools 3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>project_challenges_5_choices</t>
+          <t>project_tools_7_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>project_tools_4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>project tools 4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>project_challenges_5_choices</t>
+          <t>project_tools_7_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>project_tools_5</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>project tools 5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>project_challenges_5_choices</t>
+          <t>project_tools_7_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>project_tools_6</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>project tools 6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>project_challenges_5_choices</t>
+          <t>project_tools_7_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>project_tools_7</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>project tools 7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>project_challenges_5_choices</t>
+          <t>project_tools_7_choices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>project_tools_8</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>project tools 8</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project_tools_9</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project tools 9</t>
         </is>
       </c>
     </row>
@@ -2593,148 +2593,148 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project_tools_10</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project tools 10</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>project_tools_7_choices</t>
+          <t>project_tools_8_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project_tools_1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project tools 1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>project_tools_7_choices</t>
+          <t>project_tools_8_choices</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project_tools_2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project tools 2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>project_tools_7_choices</t>
+          <t>project_tools_8_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project_tools_3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project tools 3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>project_tools_7_choices</t>
+          <t>project_tools_8_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project_tools_4</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project tools 4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>project_tools_7_choices</t>
+          <t>project_tools_8_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project_tools_5</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project tools 5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>project_tools_7_choices</t>
+          <t>project_tools_8_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project_tools_6</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project tools 6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>project_tools_7_choices</t>
+          <t>project_tools_8_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project_tools_7</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project tools 7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>project_tools_7_choices</t>
+          <t>project_tools_8_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project_tools_8</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project tools 8</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project_tools_9</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project tools 9</t>
         </is>
       </c>
     </row>
@@ -2763,148 +2763,148 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project_tools_10</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project tools 10</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>project_tools_8_choices</t>
+          <t>project_tools_9_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project_tools_1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project tools 1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>project_tools_8_choices</t>
+          <t>project_tools_9_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project_tools_2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project tools 2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>project_tools_8_choices</t>
+          <t>project_tools_9_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project_tools_3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project tools 3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>project_tools_8_choices</t>
+          <t>project_tools_9_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project_tools_4</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project tools 4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>project_tools_8_choices</t>
+          <t>project_tools_9_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project_tools_5</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project tools 5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>project_tools_8_choices</t>
+          <t>project_tools_9_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project_tools_6</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project tools 6</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>project_tools_8_choices</t>
+          <t>project_tools_9_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project_tools_7</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project tools 7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>project_tools_8_choices</t>
+          <t>project_tools_9_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project_tools_8</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project tools 8</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project_tools_9</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project tools 9</t>
         </is>
       </c>
     </row>
@@ -2933,148 +2933,148 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project_tools_10</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project tools 10</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>project_tools_9_choices</t>
+          <t>project_tools_10_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project_tools_1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>project tools 1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>project_tools_9_choices</t>
+          <t>project_tools_10_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project_tools_2</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>project tools 2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>project_tools_9_choices</t>
+          <t>project_tools_10_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project_tools_3</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>project tools 3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>project_tools_9_choices</t>
+          <t>project_tools_10_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project_tools_4</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>project tools 4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>project_tools_9_choices</t>
+          <t>project_tools_10_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project_tools_5</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>project tools 5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>project_tools_9_choices</t>
+          <t>project_tools_10_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project_tools_6</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>project tools 6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>project_tools_9_choices</t>
+          <t>project_tools_10_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project_tools_7</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>project tools 7</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>project_tools_9_choices</t>
+          <t>project_tools_10_choices</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project_tools_8</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>project tools 8</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project_tools_9</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>project_tools_1</t>
+          <t>project tools 9</t>
         </is>
       </c>
     </row>
@@ -3103,828 +3103,692 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project_tools_10</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>project_tools_2</t>
+          <t>project tools 10</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>project_tools_10_choices</t>
+          <t>project_challenges_6_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>project_tools_3</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>project_tools_10_choices</t>
+          <t>project_challenges_6_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>project_tools_4</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>project_tools_10_choices</t>
+          <t>project_challenges_6_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>project_tools_5</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>project_tools_10_choices</t>
+          <t>project_challenges_6_choices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>project_tools_6</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>project_tools_10_choices</t>
+          <t>project_challenges_6_choices</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>project_tools_7</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>project_tools_10_choices</t>
+          <t>project_challenges_7_choices</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>project_tools_8</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>project_tools_10_choices</t>
+          <t>project_challenges_7_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>project_tools_9</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>project_tools_10_choices</t>
+          <t>project_challenges_7_choices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>project_tools_10</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>project_challenges_6_choices</t>
+          <t>project_challenges_7_choices</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>project_challenges_6_choices</t>
+          <t>project_challenges_7_choices</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>project_challenges_6_choices</t>
+          <t>project_challenges_8_choices</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>project_challenges_6_choices</t>
+          <t>project_challenges_8_choices</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>project_challenges_6_choices</t>
+          <t>project_challenges_8_choices</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>project_challenges_7_choices</t>
+          <t>project_challenges_8_choices</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>project_challenges_7_choices</t>
+          <t>project_challenges_8_choices</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>project_challenges_7_choices</t>
+          <t>project_challenges_9_choices</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>project_challenges_7_choices</t>
+          <t>project_challenges_9_choices</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>project_challenges_7_choices</t>
+          <t>project_challenges_9_choices</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>project_challenges_8_choices</t>
+          <t>project_challenges_9_choices</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>project_challenges_8_choices</t>
+          <t>project_challenges_9_choices</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>project_challenges_8_choices</t>
+          <t>project_challenges_10_choices</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>project_challenges_8_choices</t>
+          <t>project_challenges_10_choices</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>project_challenges_8_choices</t>
+          <t>project_challenges_10_choices</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>project_challenges_9_choices</t>
+          <t>project_challenges_10_choices</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>project_challenges_9_choices</t>
+          <t>project_challenges_10_choices</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>project_challenges_9_choices</t>
+          <t>project_challenges_11_choices</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>project_challenges_9_choices</t>
+          <t>project_challenges_11_choices</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>project_challenges_9_choices</t>
+          <t>project_challenges_11_choices</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>project_challenges_10_choices</t>
+          <t>project_challenges_11_choices</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>project_challenges_10_choices</t>
+          <t>project_challenges_11_choices</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>project_challenges_10_choices</t>
+          <t>project_challenges_12_choices</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>project_challenges_10_choices</t>
+          <t>project_challenges_12_choices</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>project_challenges_10_choices</t>
+          <t>project_challenges_12_choices</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>project_challenges_11_choices</t>
+          <t>project_challenges_12_choices</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>project_challenges_11_choices</t>
+          <t>project_challenges_12_choices</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>project_challenges_11_choices</t>
+          <t>project_challenges_13_choices</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges_faced_1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>challenges_faced_3</t>
+          <t>challenges faced 1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>project_challenges_11_choices</t>
+          <t>project_challenges_13_choices</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges_faced_2</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>challenges_faced_4</t>
+          <t>challenges faced 2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>project_challenges_11_choices</t>
+          <t>project_challenges_13_choices</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges_faced_3</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>challenges_faced_5</t>
+          <t>challenges faced 3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>project_challenges_12_choices</t>
+          <t>project_challenges_13_choices</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges_faced_4</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>challenges_faced_1</t>
+          <t>challenges faced 4</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>project_challenges_12_choices</t>
+          <t>project_challenges_13_choices</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
+          <t>challenges_faced_5</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>challenges_faced_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>project_challenges_12_choices</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>challenges_faced_3</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>challenges_faced_3</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>project_challenges_12_choices</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>challenges_faced_4</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>challenges_faced_4</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>project_challenges_12_choices</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>challenges_faced_5</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>challenges_faced_5</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>project_challenges_13_choices</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>challenges_faced_1</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>challenges_faced_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>project_challenges_13_choices</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>challenges_faced_2</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>challenges_faced_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>project_challenges_13_choices</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>challenges_faced_3</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>challenges_faced_3</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>project_challenges_13_choices</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>challenges_faced_4</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>challenges_faced_4</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>project_challenges_13_choices</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>challenges_faced_5</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>challenges_faced_5</t>
+          <t>challenges faced 5</t>
         </is>
       </c>
     </row>
